--- a/Faculty_Performance_Criteria_Aligned.xlsx
+++ b/Faculty_Performance_Criteria_Aligned.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Unavailable for assigned duties; frequently cancels clinic or does not meet expected days/hours</t>
+          <t>Unavailable for assigned duties; frequently cancels clinic or does not meet expected days/hours; refuses patients despite open slots; overly rigid patient population criteria</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
